--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\TESIS\armado tesina\codigo\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B1A89B-96F8-4E83-A7E7-741D07E48306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="34">
   <si>
     <t>configuracion</t>
   </si>
@@ -127,8 +121,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,13 +174,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -194,21 +185,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +229,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -280,7 +263,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -315,10 +297,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -491,15 +472,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W241"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -590,14 +567,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G2">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L2" t="s">
         <v>33</v>
       </c>
@@ -635,7 +618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -655,14 +638,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G3">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L3" t="s">
         <v>29</v>
       </c>
@@ -676,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -700,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -720,14 +709,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G4">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L4" t="s">
         <v>33</v>
       </c>
@@ -765,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -785,14 +780,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G5">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L5" t="s">
         <v>29</v>
       </c>
@@ -806,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -830,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -850,14 +851,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G6">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L6" t="s">
         <v>33</v>
       </c>
@@ -871,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -895,7 +902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -915,14 +922,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G7">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
       </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
       <c r="L7" t="s">
         <v>33</v>
       </c>
@@ -933,13 +946,13 @@
         <v>27</v>
       </c>
       <c r="O7">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -960,7 +973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -980,14 +993,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G8">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
       </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L8" t="s">
         <v>33</v>
       </c>
@@ -1025,7 +1044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1045,14 +1064,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G9">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L9" t="s">
         <v>29</v>
       </c>
@@ -1066,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1090,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1110,14 +1135,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G10">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
       </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L10" t="s">
         <v>33</v>
       </c>
@@ -1155,7 +1186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1175,14 +1206,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G11">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L11" t="s">
         <v>33</v>
       </c>
@@ -1196,10 +1233,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P11">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
@@ -1220,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1240,14 +1277,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G12">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L12" t="s">
         <v>33</v>
       </c>
@@ -1258,10 +1301,10 @@
         <v>30</v>
       </c>
       <c r="O12">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P12">
-        <v>0.59167277858232747</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1285,7 +1328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1305,19 +1348,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G13">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L13" t="s">
         <v>30</v>
       </c>
       <c r="M13">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -1326,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -1350,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1370,14 +1419,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G14">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="L14" t="s">
         <v>33</v>
       </c>
@@ -1388,7 +1443,7 @@
         <v>30</v>
       </c>
       <c r="O14">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P14">
         <v>0.863120568566631</v>
@@ -1415,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1426,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1435,14 +1490,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G15">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
       <c r="L15" t="s">
         <v>33</v>
       </c>
@@ -1453,13 +1514,13 @@
         <v>30</v>
       </c>
       <c r="O15">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="b">
         <v>1</v>
@@ -1480,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1500,14 +1561,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G16">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
       </c>
+      <c r="J16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L16" t="s">
         <v>31</v>
       </c>
@@ -1521,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -1545,7 +1612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1565,14 +1632,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G17">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
       </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L17" t="s">
         <v>33</v>
       </c>
@@ -1610,7 +1683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1630,14 +1703,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G18">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
       </c>
+      <c r="J18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L18" t="s">
         <v>33</v>
       </c>
@@ -1651,7 +1730,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="P18">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -1675,7 +1754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1695,14 +1774,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G19">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H19">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
       </c>
+      <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L19" t="s">
         <v>33</v>
       </c>
@@ -1716,10 +1801,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P19">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
@@ -1740,7 +1825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1760,14 +1845,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G20">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H20">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
       </c>
+      <c r="J20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
       <c r="L20" t="s">
         <v>33</v>
       </c>
@@ -1784,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
@@ -1805,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1825,14 +1916,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G21">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H21">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
       </c>
+      <c r="J21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L21" t="s">
         <v>33</v>
       </c>
@@ -1846,7 +1943,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="P21">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -1870,7 +1967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1890,14 +1987,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G22">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
+      <c r="J22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L22" t="s">
         <v>29</v>
       </c>
@@ -1911,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -1935,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1955,14 +2058,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G23">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
       </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L23" t="s">
         <v>29</v>
       </c>
@@ -1976,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -2000,7 +2109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2011,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2020,14 +2129,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G24">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
       </c>
+      <c r="J24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L24" t="s">
         <v>33</v>
       </c>
@@ -2041,10 +2156,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
@@ -2056,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2065,7 +2180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2085,14 +2200,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G25">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
       </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L25" t="s">
         <v>33</v>
       </c>
@@ -2130,7 +2251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2150,14 +2271,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G26">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
       </c>
+      <c r="J26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L26" t="s">
         <v>33</v>
       </c>
@@ -2168,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="O26">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P26">
         <v>0.863120568566631</v>
@@ -2195,7 +2322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2206,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -2215,14 +2342,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G27">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H27">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
       </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
       <c r="L27" t="s">
         <v>33</v>
       </c>
@@ -2233,13 +2366,13 @@
         <v>30</v>
       </c>
       <c r="O27">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="b">
         <v>1</v>
@@ -2260,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2271,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2280,14 +2413,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G28">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
       </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
       <c r="L28" t="s">
         <v>33</v>
       </c>
@@ -2298,13 +2437,13 @@
         <v>30</v>
       </c>
       <c r="O28">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
@@ -2325,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2336,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -2345,14 +2484,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G29">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
       </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L29" t="s">
         <v>33</v>
       </c>
@@ -2363,13 +2508,13 @@
         <v>30</v>
       </c>
       <c r="O29">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P29">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="b">
         <v>1</v>
@@ -2381,7 +2526,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2390,7 +2535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2410,14 +2555,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G30">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H30">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
       </c>
+      <c r="J30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L30" t="s">
         <v>33</v>
       </c>
@@ -2431,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -2455,7 +2606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2475,14 +2626,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G31">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H31">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
       </c>
+      <c r="J31" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L31" t="s">
         <v>33</v>
       </c>
@@ -2520,7 +2677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2531,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -2540,14 +2697,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G32">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H32">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
       </c>
+      <c r="J32" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L32" t="s">
         <v>33</v>
       </c>
@@ -2561,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="b">
         <v>1</v>
@@ -2576,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2585,7 +2748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -2605,14 +2768,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G33">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
       </c>
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
       <c r="L33" t="s">
         <v>33</v>
       </c>
@@ -2629,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="b">
         <v>1</v>
@@ -2650,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2670,14 +2839,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G34">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
       </c>
+      <c r="J34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L34" t="s">
         <v>33</v>
       </c>
@@ -2691,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -2715,7 +2890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2726,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -2735,14 +2910,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G35">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H35">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
       </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
       <c r="L35" t="s">
         <v>33</v>
       </c>
@@ -2759,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
@@ -2780,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2800,14 +2981,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G36">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H36">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
       </c>
+      <c r="J36" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
       <c r="L36" t="s">
         <v>33</v>
       </c>
@@ -2824,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="b">
         <v>1</v>
@@ -2845,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -2865,14 +3052,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G37">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H37">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
       </c>
+      <c r="J37" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L37" t="s">
         <v>29</v>
       </c>
@@ -2910,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -2930,14 +3123,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G38">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H38">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
       </c>
+      <c r="J38" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L38" t="s">
         <v>33</v>
       </c>
@@ -2975,7 +3174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2995,19 +3194,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G39">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H39">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
       </c>
+      <c r="J39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L39" t="s">
         <v>30</v>
       </c>
       <c r="M39">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N39" t="s">
         <v>29</v>
@@ -3016,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
@@ -3040,7 +3245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3060,14 +3265,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G40">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
       </c>
+      <c r="J40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L40" t="s">
         <v>33</v>
       </c>
@@ -3081,10 +3292,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="P40">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="b">
         <v>1</v>
@@ -3105,7 +3316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -3116,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="D41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>7</v>
@@ -3125,14 +3336,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G41">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H41">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
       </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L41" t="s">
         <v>33</v>
       </c>
@@ -3146,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="b">
         <v>1</v>
@@ -3161,7 +3378,7 @@
         <v>7</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3170,7 +3387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -3190,14 +3407,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G42">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H42">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
       </c>
+      <c r="J42" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L42" t="s">
         <v>33</v>
       </c>
@@ -3235,7 +3458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -3255,14 +3478,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G43">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H43">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
       </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
       <c r="L43" t="s">
         <v>33</v>
       </c>
@@ -3279,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="b">
         <v>1</v>
@@ -3300,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -3320,14 +3549,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G44">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H44">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
       </c>
+      <c r="J44" t="s">
+        <v>28</v>
+      </c>
+      <c r="K44">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L44" t="s">
         <v>26</v>
       </c>
@@ -3341,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
@@ -3365,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -3385,14 +3620,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G45">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H45">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
       </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L45" t="s">
         <v>29</v>
       </c>
@@ -3406,10 +3647,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -3430,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -3450,19 +3691,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G46">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H46">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
       </c>
+      <c r="J46" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L46" t="s">
         <v>30</v>
       </c>
       <c r="M46">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N46" t="s">
         <v>29</v>
@@ -3471,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
@@ -3495,7 +3742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -3515,14 +3762,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G47">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H47">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
       </c>
+      <c r="J47" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L47" t="s">
         <v>29</v>
       </c>
@@ -3560,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -3580,14 +3833,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G48">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
       </c>
+      <c r="J48" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L48" t="s">
         <v>33</v>
       </c>
@@ -3625,7 +3884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -3645,14 +3904,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G49">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H49">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
       </c>
+      <c r="J49" t="s">
+        <v>28</v>
+      </c>
+      <c r="K49">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L49" t="s">
         <v>33</v>
       </c>
@@ -3666,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -3690,7 +3955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23">
       <c r="A50" t="s">
         <v>23</v>
       </c>
@@ -3710,14 +3975,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G50">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
       </c>
+      <c r="J50" t="s">
+        <v>27</v>
+      </c>
+      <c r="K50">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L50" t="s">
         <v>33</v>
       </c>
@@ -3728,10 +3999,10 @@
         <v>30</v>
       </c>
       <c r="O50">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P50">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -3755,7 +4026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -3775,14 +4046,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G51">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H51">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
       </c>
+      <c r="J51" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
       <c r="L51" t="s">
         <v>33</v>
       </c>
@@ -3799,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="b">
         <v>1</v>
@@ -3820,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -3831,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="D52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>7</v>
@@ -3840,14 +4117,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G52">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H52">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
       </c>
+      <c r="J52" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L52" t="s">
         <v>33</v>
       </c>
@@ -3861,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="b">
         <v>1</v>
@@ -3876,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="V52">
         <v>7</v>
@@ -3885,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -3905,14 +4188,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G53">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H53">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
       </c>
+      <c r="J53" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L53" t="s">
         <v>29</v>
       </c>
@@ -3950,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -3970,14 +4259,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G54">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
       </c>
+      <c r="J54" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L54" t="s">
         <v>33</v>
       </c>
@@ -4015,7 +4310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -4026,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <v>7</v>
@@ -4035,14 +4330,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G55">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
       </c>
+      <c r="J55" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L55" t="s">
         <v>33</v>
       </c>
@@ -4056,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
@@ -4071,7 +4372,7 @@
         <v>7</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="V55">
         <v>7</v>
@@ -4080,7 +4381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -4100,14 +4401,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G56">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H56">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
       </c>
+      <c r="J56" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L56" t="s">
         <v>33</v>
       </c>
@@ -4145,7 +4452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23">
       <c r="A57" t="s">
         <v>23</v>
       </c>
@@ -4165,14 +4472,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G57">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H57">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
       </c>
+      <c r="J57" t="s">
+        <v>28</v>
+      </c>
+      <c r="K57">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L57" t="s">
         <v>29</v>
       </c>
@@ -4186,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -4210,7 +4523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -4221,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -4230,14 +4543,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G58">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H58">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
       </c>
+      <c r="J58" t="s">
+        <v>30</v>
+      </c>
+      <c r="K58">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L58" t="s">
         <v>33</v>
       </c>
@@ -4251,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="b">
         <v>1</v>
@@ -4266,7 +4585,7 @@
         <v>7</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="V58">
         <v>7</v>
@@ -4275,7 +4594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -4295,14 +4614,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G59">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H59">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
       </c>
+      <c r="J59" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L59" t="s">
         <v>29</v>
       </c>
@@ -4316,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.59167277858232747</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -4340,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -4351,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="D60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>7</v>
@@ -4360,14 +4685,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G60">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
       </c>
+      <c r="J60" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
       <c r="L60" t="s">
         <v>33</v>
       </c>
@@ -4378,13 +4709,13 @@
         <v>30</v>
       </c>
       <c r="O60">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P60">
         <v>0</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="b">
         <v>1</v>
@@ -4405,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -4425,14 +4756,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G61">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H61">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>27</v>
+      </c>
+      <c r="K61">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L61" t="s">
         <v>33</v>
       </c>
@@ -4446,7 +4783,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="P61">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4470,7 +4807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -4490,14 +4827,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G62">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
       </c>
+      <c r="J62" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L62" t="s">
         <v>33</v>
       </c>
@@ -4535,7 +4878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -4555,14 +4898,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G63">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H63">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
       </c>
+      <c r="J63" t="s">
+        <v>30</v>
+      </c>
+      <c r="K63">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L63" t="s">
         <v>33</v>
       </c>
@@ -4576,10 +4925,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P63">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="b">
         <v>1</v>
@@ -4600,7 +4949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -4620,14 +4969,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G64">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H64">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
       </c>
+      <c r="J64" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L64" t="s">
         <v>29</v>
       </c>
@@ -4641,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>0.59167277858232747</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -4665,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -4685,14 +5040,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G65">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
       </c>
+      <c r="J65" t="s">
+        <v>27</v>
+      </c>
+      <c r="K65">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L65" t="s">
         <v>33</v>
       </c>
@@ -4706,7 +5067,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="P65">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -4730,7 +5091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -4750,14 +5111,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G66">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
       </c>
+      <c r="J66" t="s">
+        <v>27</v>
+      </c>
+      <c r="K66">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L66" t="s">
         <v>29</v>
       </c>
@@ -4771,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
@@ -4795,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -4815,14 +5182,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G67">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H67">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
       </c>
+      <c r="J67" t="s">
+        <v>30</v>
+      </c>
+      <c r="K67">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L67" t="s">
         <v>33</v>
       </c>
@@ -4836,10 +5209,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P67">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -4860,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23">
       <c r="A68" t="s">
         <v>23</v>
       </c>
@@ -4880,14 +5253,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G68">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
       </c>
+      <c r="J68" t="s">
+        <v>28</v>
+      </c>
+      <c r="K68">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L68" t="s">
         <v>33</v>
       </c>
@@ -4901,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -4925,7 +5304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23">
       <c r="A69" t="s">
         <v>23</v>
       </c>
@@ -4945,19 +5324,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G69">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H69">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
+      <c r="J69" t="s">
+        <v>28</v>
+      </c>
+      <c r="K69">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L69" t="s">
         <v>30</v>
       </c>
       <c r="M69">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N69" t="s">
         <v>29</v>
@@ -4966,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
@@ -4990,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -5010,14 +5395,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G70">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H70">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
       </c>
+      <c r="J70" t="s">
+        <v>27</v>
+      </c>
+      <c r="K70">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L70" t="s">
         <v>33</v>
       </c>
@@ -5031,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="P70">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -5055,7 +5446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -5075,14 +5466,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G71">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H71">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
       </c>
+      <c r="J71" t="s">
+        <v>27</v>
+      </c>
+      <c r="K71">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L71" t="s">
         <v>33</v>
       </c>
@@ -5093,10 +5490,10 @@
         <v>30</v>
       </c>
       <c r="O71">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P71">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -5120,7 +5517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -5140,14 +5537,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G72">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
       </c>
+      <c r="J72" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L72" t="s">
         <v>33</v>
       </c>
@@ -5185,7 +5588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -5196,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="D73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>7</v>
@@ -5205,14 +5608,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G73">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H73">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
       </c>
+      <c r="J73" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
       <c r="L73" t="s">
         <v>33</v>
       </c>
@@ -5229,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -5250,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23">
       <c r="A74" t="s">
         <v>23</v>
       </c>
@@ -5270,14 +5679,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G74">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H74">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
       </c>
+      <c r="J74" t="s">
+        <v>26</v>
+      </c>
+      <c r="K74">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L74" t="s">
         <v>33</v>
       </c>
@@ -5288,7 +5703,7 @@
         <v>30</v>
       </c>
       <c r="O74">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P74">
         <v>0.863120568566631</v>
@@ -5315,7 +5730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -5335,14 +5750,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G75">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H75">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
+      <c r="J75" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
       <c r="L75" t="s">
         <v>33</v>
       </c>
@@ -5359,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -5380,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23">
       <c r="A76" t="s">
         <v>23</v>
       </c>
@@ -5400,14 +5821,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G76">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H76">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
       <c r="L76" t="s">
         <v>33</v>
       </c>
@@ -5424,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -5445,7 +5872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -5465,14 +5892,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G77">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
       </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L77" t="s">
         <v>33</v>
       </c>
@@ -5486,10 +5919,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P77">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -5510,7 +5943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23">
       <c r="A78" t="s">
         <v>23</v>
       </c>
@@ -5530,14 +5963,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G78">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
       </c>
+      <c r="J78" t="s">
+        <v>27</v>
+      </c>
+      <c r="K78">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L78" t="s">
         <v>29</v>
       </c>
@@ -5551,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
@@ -5575,7 +6014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -5595,14 +6034,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G79">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H79">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
       </c>
+      <c r="J79" t="s">
+        <v>27</v>
+      </c>
+      <c r="K79">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L79" t="s">
         <v>33</v>
       </c>
@@ -5613,10 +6058,10 @@
         <v>27</v>
       </c>
       <c r="O79">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P79">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
@@ -5640,7 +6085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23">
       <c r="A80" t="s">
         <v>23</v>
       </c>
@@ -5660,14 +6105,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G80">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H80">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
       </c>
+      <c r="J80" t="s">
+        <v>28</v>
+      </c>
+      <c r="K80">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L80" t="s">
         <v>33</v>
       </c>
@@ -5681,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -5705,7 +6156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -5725,19 +6176,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G81">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H81">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
       </c>
+      <c r="J81" t="s">
+        <v>28</v>
+      </c>
+      <c r="K81">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L81" t="s">
         <v>30</v>
       </c>
       <c r="M81">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N81" t="s">
         <v>29</v>
@@ -5746,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="P81">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -5770,7 +6227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -5790,14 +6247,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G82">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
       </c>
+      <c r="J82" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L82" t="s">
         <v>33</v>
       </c>
@@ -5835,7 +6298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -5846,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="D83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>7</v>
@@ -5855,14 +6318,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G83">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H83">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
       </c>
+      <c r="J83" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
       <c r="L83" t="s">
         <v>33</v>
       </c>
@@ -5879,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -5900,7 +6369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -5911,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="D84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>7</v>
@@ -5920,14 +6389,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G84">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
       </c>
+      <c r="J84" t="s">
+        <v>29</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
       <c r="L84" t="s">
         <v>33</v>
       </c>
@@ -5944,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -5965,7 +6440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -5985,14 +6460,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G85">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H85">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
       </c>
+      <c r="J85" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
       <c r="L85" t="s">
         <v>33</v>
       </c>
@@ -6009,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -6030,7 +6511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -6041,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>7</v>
@@ -6050,14 +6531,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G86">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H86">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
       </c>
+      <c r="J86" t="s">
+        <v>29</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
       <c r="L86" t="s">
         <v>33</v>
       </c>
@@ -6074,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -6095,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -6115,14 +6602,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G87">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
       </c>
+      <c r="J87" t="s">
+        <v>29</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
       <c r="L87" t="s">
         <v>33</v>
       </c>
@@ -6139,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -6160,7 +6653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -6180,14 +6673,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G88">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H88">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
       </c>
+      <c r="J88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L88" t="s">
         <v>33</v>
       </c>
@@ -6225,7 +6724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -6236,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="D89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>7</v>
@@ -6245,14 +6744,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G89">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H89">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
       </c>
+      <c r="J89" t="s">
+        <v>29</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
       <c r="L89" t="s">
         <v>33</v>
       </c>
@@ -6269,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -6290,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23">
       <c r="A90" t="s">
         <v>23</v>
       </c>
@@ -6310,14 +6815,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G90">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
       </c>
+      <c r="J90" t="s">
+        <v>26</v>
+      </c>
+      <c r="K90">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L90" t="s">
         <v>29</v>
       </c>
@@ -6355,7 +6866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -6375,14 +6886,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G91">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
       </c>
+      <c r="J91" t="s">
+        <v>27</v>
+      </c>
+      <c r="K91">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L91" t="s">
         <v>33</v>
       </c>
@@ -6396,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
@@ -6420,7 +6937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -6440,19 +6957,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G92">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
       </c>
+      <c r="J92" t="s">
+        <v>27</v>
+      </c>
+      <c r="K92">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L92" t="s">
         <v>30</v>
       </c>
       <c r="M92">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N92" t="s">
         <v>29</v>
@@ -6461,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
@@ -6485,7 +7008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -6496,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>7</v>
@@ -6505,14 +7028,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G93">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
       </c>
+      <c r="J93" t="s">
+        <v>29</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
       <c r="L93" t="s">
         <v>33</v>
       </c>
@@ -6529,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -6550,7 +7079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -6570,19 +7099,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G94">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H94">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
       </c>
+      <c r="J94" t="s">
+        <v>28</v>
+      </c>
+      <c r="K94">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L94" t="s">
         <v>30</v>
       </c>
       <c r="M94">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N94" t="s">
         <v>29</v>
@@ -6591,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -6615,7 +7150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -6626,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="D95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>7</v>
@@ -6635,14 +7170,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G95">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H95">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
       </c>
+      <c r="J95" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
       <c r="L95" t="s">
         <v>33</v>
       </c>
@@ -6659,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -6680,7 +7221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -6700,14 +7241,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G96">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H96">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
       </c>
+      <c r="J96" t="s">
+        <v>26</v>
+      </c>
+      <c r="K96">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L96" t="s">
         <v>33</v>
       </c>
@@ -6745,7 +7292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -6756,7 +7303,7 @@
         <v>1</v>
       </c>
       <c r="D97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>7</v>
@@ -6765,14 +7312,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G97">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
       </c>
+      <c r="J97" t="s">
+        <v>30</v>
+      </c>
+      <c r="K97">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L97" t="s">
         <v>33</v>
       </c>
@@ -6786,10 +7339,10 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -6801,7 +7354,7 @@
         <v>7</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="V97">
         <v>7</v>
@@ -6810,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -6830,14 +7383,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G98">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
       </c>
+      <c r="J98" t="s">
+        <v>26</v>
+      </c>
+      <c r="K98">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L98" t="s">
         <v>33</v>
       </c>
@@ -6848,7 +7407,7 @@
         <v>30</v>
       </c>
       <c r="O98">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P98">
         <v>0.863120568566631</v>
@@ -6875,7 +7434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -6895,14 +7454,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G99">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H99">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
       </c>
+      <c r="J99" t="s">
+        <v>29</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
       <c r="L99" t="s">
         <v>33</v>
       </c>
@@ -6919,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -6940,7 +7505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -6951,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="D100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>7</v>
@@ -6960,14 +7525,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G100">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
       </c>
+      <c r="J100" t="s">
+        <v>29</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
       <c r="L100" t="s">
         <v>33</v>
       </c>
@@ -6984,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -7005,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -7025,14 +7596,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G101">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H101">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
       </c>
+      <c r="J101" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L101" t="s">
         <v>33</v>
       </c>
@@ -7043,10 +7620,10 @@
         <v>27</v>
       </c>
       <c r="O101">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P101">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
@@ -7070,7 +7647,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -7090,14 +7667,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G102">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
       </c>
+      <c r="J102" t="s">
+        <v>26</v>
+      </c>
+      <c r="K102">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L102" t="s">
         <v>33</v>
       </c>
@@ -7135,7 +7718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -7155,14 +7738,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G103">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H103">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
       </c>
+      <c r="J103" t="s">
+        <v>30</v>
+      </c>
+      <c r="K103">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L103" t="s">
         <v>33</v>
       </c>
@@ -7176,10 +7765,10 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="P103">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -7200,7 +7789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23">
       <c r="A104" t="s">
         <v>23</v>
       </c>
@@ -7211,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -7220,14 +7809,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G104">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
       </c>
+      <c r="J104" t="s">
+        <v>30</v>
+      </c>
+      <c r="K104">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L104" t="s">
         <v>33</v>
       </c>
@@ -7241,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -7256,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="V104">
         <v>7</v>
@@ -7265,7 +7860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23">
       <c r="A105" t="s">
         <v>23</v>
       </c>
@@ -7276,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="D105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>7</v>
@@ -7285,14 +7880,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G105">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H105">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
       </c>
+      <c r="J105" t="s">
+        <v>29</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
       <c r="L105" t="s">
         <v>33</v>
       </c>
@@ -7309,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -7330,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23">
       <c r="A106" t="s">
         <v>23</v>
       </c>
@@ -7350,14 +7951,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G106">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H106">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
       </c>
+      <c r="J106" t="s">
+        <v>28</v>
+      </c>
+      <c r="K106">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L106" t="s">
         <v>26</v>
       </c>
@@ -7371,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q106" t="b">
         <v>0</v>
@@ -7395,7 +8002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23">
       <c r="A107" t="s">
         <v>23</v>
       </c>
@@ -7415,14 +8022,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G107">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H107">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
       </c>
+      <c r="J107" t="s">
+        <v>30</v>
+      </c>
+      <c r="K107">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L107" t="s">
         <v>33</v>
       </c>
@@ -7436,10 +8049,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P107">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="b">
         <v>1</v>
@@ -7460,7 +8073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23">
       <c r="A108" t="s">
         <v>23</v>
       </c>
@@ -7480,14 +8093,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G108">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H108">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I108" t="s">
         <v>15</v>
       </c>
+      <c r="J108" t="s">
+        <v>29</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
       <c r="L108" t="s">
         <v>33</v>
       </c>
@@ -7504,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="Q108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="b">
         <v>1</v>
@@ -7525,7 +8144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23">
       <c r="A109" t="s">
         <v>23</v>
       </c>
@@ -7545,14 +8164,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G109">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H109">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
       </c>
+      <c r="J109" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
       <c r="L109" t="s">
         <v>33</v>
       </c>
@@ -7569,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="Q109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="b">
         <v>1</v>
@@ -7590,7 +8215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23">
       <c r="A110" t="s">
         <v>23</v>
       </c>
@@ -7610,14 +8235,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G110">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H110">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
       </c>
+      <c r="J110" t="s">
+        <v>26</v>
+      </c>
+      <c r="K110">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L110" t="s">
         <v>28</v>
       </c>
@@ -7655,7 +8286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23">
       <c r="A111" t="s">
         <v>23</v>
       </c>
@@ -7675,14 +8306,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G111">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H111">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
       </c>
+      <c r="J111" t="s">
+        <v>27</v>
+      </c>
+      <c r="K111">
+        <v>0.4285714285714285</v>
+      </c>
       <c r="L111" t="s">
         <v>33</v>
       </c>
@@ -7696,7 +8333,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="P111">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q111" t="b">
         <v>0</v>
@@ -7720,7 +8357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23">
       <c r="A112" t="s">
         <v>23</v>
       </c>
@@ -7731,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>7</v>
@@ -7740,14 +8377,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G112">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H112">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I112" t="s">
         <v>15</v>
       </c>
+      <c r="J112" t="s">
+        <v>30</v>
+      </c>
+      <c r="K112">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L112" t="s">
         <v>33</v>
       </c>
@@ -7761,10 +8404,10 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="b">
         <v>1</v>
@@ -7776,7 +8419,7 @@
         <v>7</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="V112">
         <v>7</v>
@@ -7785,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23">
       <c r="A113" t="s">
         <v>23</v>
       </c>
@@ -7805,14 +8448,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G113">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H113">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I113" t="s">
         <v>15</v>
       </c>
+      <c r="J113" t="s">
+        <v>26</v>
+      </c>
+      <c r="K113">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L113" t="s">
         <v>33</v>
       </c>
@@ -7850,7 +8499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23">
       <c r="A114" t="s">
         <v>23</v>
       </c>
@@ -7861,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>7</v>
@@ -7870,14 +8519,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G114">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H114">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
       </c>
+      <c r="J114" t="s">
+        <v>30</v>
+      </c>
+      <c r="K114">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L114" t="s">
         <v>33</v>
       </c>
@@ -7891,10 +8546,10 @@
         <v>0</v>
       </c>
       <c r="P114">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="b">
         <v>1</v>
@@ -7906,7 +8561,7 @@
         <v>7</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="V114">
         <v>7</v>
@@ -7915,7 +8570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23">
       <c r="A115" t="s">
         <v>23</v>
       </c>
@@ -7935,14 +8590,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G115">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H115">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I115" t="s">
         <v>15</v>
       </c>
+      <c r="J115" t="s">
+        <v>28</v>
+      </c>
+      <c r="K115">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L115" t="s">
         <v>33</v>
       </c>
@@ -7953,10 +8614,10 @@
         <v>30</v>
       </c>
       <c r="O115">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P115">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q115" t="b">
         <v>0</v>
@@ -7980,7 +8641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23">
       <c r="A116" t="s">
         <v>23</v>
       </c>
@@ -8000,14 +8661,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G116">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
       </c>
+      <c r="J116" t="s">
+        <v>30</v>
+      </c>
+      <c r="K116">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L116" t="s">
         <v>33</v>
       </c>
@@ -8021,10 +8688,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P116">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" t="b">
         <v>1</v>
@@ -8045,7 +8712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23">
       <c r="A117" t="s">
         <v>23</v>
       </c>
@@ -8065,14 +8732,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G117">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H117">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I117" t="s">
         <v>15</v>
       </c>
+      <c r="J117" t="s">
+        <v>30</v>
+      </c>
+      <c r="K117">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L117" t="s">
         <v>33</v>
       </c>
@@ -8086,10 +8759,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="P117">
-        <v>0.59167277858232725</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="Q117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" t="b">
         <v>1</v>
@@ -8110,7 +8783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23">
       <c r="A118" t="s">
         <v>23</v>
       </c>
@@ -8130,19 +8803,25 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G118">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H118">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I118" t="s">
         <v>15</v>
       </c>
+      <c r="J118" t="s">
+        <v>28</v>
+      </c>
+      <c r="K118">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="L118" t="s">
         <v>30</v>
       </c>
       <c r="M118">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N118" t="s">
         <v>29</v>
@@ -8151,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>0.98522813603425152</v>
+        <v>0.9852281360342515</v>
       </c>
       <c r="Q118" t="b">
         <v>0</v>
@@ -8175,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23">
       <c r="A119" t="s">
         <v>23</v>
       </c>
@@ -8195,14 +8874,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G119">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H119">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
       </c>
+      <c r="J119" t="s">
+        <v>26</v>
+      </c>
+      <c r="K119">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L119" t="s">
         <v>33</v>
       </c>
@@ -8240,7 +8925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23">
       <c r="A120" t="s">
         <v>23</v>
       </c>
@@ -8260,14 +8945,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G120">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H120">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
       </c>
+      <c r="J120" t="s">
+        <v>26</v>
+      </c>
+      <c r="K120">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L120" t="s">
         <v>33</v>
       </c>
@@ -8305,7 +8996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23">
       <c r="A121" t="s">
         <v>23</v>
       </c>
@@ -8325,14 +9016,20 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G121">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="H121">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I121" t="s">
         <v>15</v>
       </c>
+      <c r="J121" t="s">
+        <v>26</v>
+      </c>
+      <c r="K121">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L121" t="s">
         <v>33</v>
       </c>
@@ -8370,7 +9067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -8390,7 +9087,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G122">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I122" t="s">
         <v>25</v>
@@ -8435,7 +9132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23">
       <c r="A123" t="s">
         <v>24</v>
       </c>
@@ -8455,7 +9152,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G123">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I123" t="s">
         <v>25</v>
@@ -8464,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="K123">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L123" t="s">
         <v>29</v>
@@ -8500,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23">
       <c r="A124" t="s">
         <v>24</v>
       </c>
@@ -8520,7 +9217,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G124">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I124" t="s">
         <v>25</v>
@@ -8565,7 +9262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23">
       <c r="A125" t="s">
         <v>24</v>
       </c>
@@ -8585,7 +9282,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G125">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I125" t="s">
         <v>25</v>
@@ -8630,7 +9327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -8650,7 +9347,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G126">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I126" t="s">
         <v>25</v>
@@ -8659,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="K126">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L126" t="s">
         <v>33</v>
@@ -8695,7 +9392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -8715,7 +9412,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G127">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I127" t="s">
         <v>25</v>
@@ -8736,7 +9433,7 @@
         <v>27</v>
       </c>
       <c r="O127">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Q127" t="b">
         <v>0</v>
@@ -8760,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23">
       <c r="A128" t="s">
         <v>24</v>
       </c>
@@ -8780,7 +9477,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G128">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I128" t="s">
         <v>25</v>
@@ -8825,7 +9522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -8845,7 +9542,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G129">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I129" t="s">
         <v>25</v>
@@ -8854,7 +9551,7 @@
         <v>30</v>
       </c>
       <c r="K129">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L129" t="s">
         <v>29</v>
@@ -8890,7 +9587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -8910,7 +9607,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G130">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I130" t="s">
         <v>25</v>
@@ -8955,7 +9652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -8975,7 +9672,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G131">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I131" t="s">
         <v>25</v>
@@ -8984,7 +9681,7 @@
         <v>30</v>
       </c>
       <c r="K131">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L131" t="s">
         <v>33</v>
@@ -9020,7 +9717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23">
       <c r="A132" t="s">
         <v>24</v>
       </c>
@@ -9040,7 +9737,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G132">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I132" t="s">
         <v>25</v>
@@ -9061,7 +9758,7 @@
         <v>30</v>
       </c>
       <c r="O132">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q132" t="b">
         <v>1</v>
@@ -9085,7 +9782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -9105,7 +9802,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G133">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I133" t="s">
         <v>25</v>
@@ -9120,7 +9817,7 @@
         <v>30</v>
       </c>
       <c r="M133">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N133" t="s">
         <v>29</v>
@@ -9150,7 +9847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23">
       <c r="A134" t="s">
         <v>24</v>
       </c>
@@ -9170,7 +9867,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G134">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I134" t="s">
         <v>25</v>
@@ -9191,7 +9888,7 @@
         <v>30</v>
       </c>
       <c r="O134">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q134" t="b">
         <v>1</v>
@@ -9215,7 +9912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -9235,7 +9932,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G135">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I135" t="s">
         <v>25</v>
@@ -9256,7 +9953,7 @@
         <v>30</v>
       </c>
       <c r="O135">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q135" t="b">
         <v>0</v>
@@ -9280,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -9300,7 +9997,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G136">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I136" t="s">
         <v>25</v>
@@ -9309,7 +10006,7 @@
         <v>27</v>
       </c>
       <c r="K136">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L136" t="s">
         <v>31</v>
@@ -9345,7 +10042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -9365,7 +10062,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G137">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I137" t="s">
         <v>25</v>
@@ -9410,7 +10107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -9430,7 +10127,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G138">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I138" t="s">
         <v>25</v>
@@ -9475,7 +10172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23">
       <c r="A139" t="s">
         <v>24</v>
       </c>
@@ -9495,7 +10192,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G139">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I139" t="s">
         <v>25</v>
@@ -9504,7 +10201,7 @@
         <v>30</v>
       </c>
       <c r="K139">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L139" t="s">
         <v>33</v>
@@ -9540,7 +10237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23">
       <c r="A140" t="s">
         <v>24</v>
       </c>
@@ -9560,7 +10257,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G140">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I140" t="s">
         <v>25</v>
@@ -9605,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23">
       <c r="A141" t="s">
         <v>24</v>
       </c>
@@ -9625,7 +10322,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G141">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I141" t="s">
         <v>25</v>
@@ -9634,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="K141">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L141" t="s">
         <v>33</v>
@@ -9670,7 +10367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23">
       <c r="A142" t="s">
         <v>24</v>
       </c>
@@ -9690,7 +10387,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G142">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I142" t="s">
         <v>25</v>
@@ -9699,7 +10396,7 @@
         <v>27</v>
       </c>
       <c r="K142">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L142" t="s">
         <v>29</v>
@@ -9735,7 +10432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23">
       <c r="A143" t="s">
         <v>24</v>
       </c>
@@ -9755,7 +10452,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G143">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I143" t="s">
         <v>25</v>
@@ -9764,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="K143">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L143" t="s">
         <v>29</v>
@@ -9800,7 +10497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -9820,7 +10517,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G144">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I144" t="s">
         <v>25</v>
@@ -9829,7 +10526,7 @@
         <v>30</v>
       </c>
       <c r="K144">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L144" t="s">
         <v>33</v>
@@ -9865,7 +10562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -9885,7 +10582,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G145">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I145" t="s">
         <v>25</v>
@@ -9930,7 +10627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -9950,7 +10647,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G146">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I146" t="s">
         <v>25</v>
@@ -9971,7 +10668,7 @@
         <v>30</v>
       </c>
       <c r="O146">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q146" t="b">
         <v>0</v>
@@ -9995,7 +10692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -10015,7 +10712,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G147">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I147" t="s">
         <v>25</v>
@@ -10036,7 +10733,7 @@
         <v>30</v>
       </c>
       <c r="O147">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q147" t="b">
         <v>0</v>
@@ -10060,7 +10757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23">
       <c r="A148" t="s">
         <v>24</v>
       </c>
@@ -10080,7 +10777,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G148">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I148" t="s">
         <v>25</v>
@@ -10101,7 +10798,7 @@
         <v>30</v>
       </c>
       <c r="O148">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q148" t="b">
         <v>0</v>
@@ -10125,7 +10822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -10145,7 +10842,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G149">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I149" t="s">
         <v>25</v>
@@ -10154,7 +10851,7 @@
         <v>30</v>
       </c>
       <c r="K149">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L149" t="s">
         <v>33</v>
@@ -10166,7 +10863,7 @@
         <v>30</v>
       </c>
       <c r="O149">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q149" t="b">
         <v>0</v>
@@ -10190,7 +10887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -10210,7 +10907,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G150">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I150" t="s">
         <v>25</v>
@@ -10255,7 +10952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -10275,7 +10972,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G151">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I151" t="s">
         <v>25</v>
@@ -10320,7 +11017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -10340,7 +11037,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G152">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I152" t="s">
         <v>25</v>
@@ -10349,7 +11046,7 @@
         <v>30</v>
       </c>
       <c r="K152">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L152" t="s">
         <v>33</v>
@@ -10385,7 +11082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -10405,7 +11102,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G153">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I153" t="s">
         <v>25</v>
@@ -10450,7 +11147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -10470,7 +11167,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G154">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I154" t="s">
         <v>25</v>
@@ -10479,7 +11176,7 @@
         <v>27</v>
       </c>
       <c r="K154">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L154" t="s">
         <v>33</v>
@@ -10515,7 +11212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23">
       <c r="A155" t="s">
         <v>24</v>
       </c>
@@ -10535,7 +11232,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G155">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I155" t="s">
         <v>25</v>
@@ -10580,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -10600,7 +11297,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G156">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I156" t="s">
         <v>25</v>
@@ -10645,7 +11342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -10665,7 +11362,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G157">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I157" t="s">
         <v>25</v>
@@ -10710,7 +11407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23">
       <c r="A158" t="s">
         <v>24</v>
       </c>
@@ -10730,7 +11427,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G158">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I158" t="s">
         <v>25</v>
@@ -10775,7 +11472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23">
       <c r="A159" t="s">
         <v>24</v>
       </c>
@@ -10795,7 +11492,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G159">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I159" t="s">
         <v>25</v>
@@ -10810,7 +11507,7 @@
         <v>30</v>
       </c>
       <c r="M159">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N159" t="s">
         <v>29</v>
@@ -10840,7 +11537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23">
       <c r="A160" t="s">
         <v>24</v>
       </c>
@@ -10860,7 +11557,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G160">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I160" t="s">
         <v>25</v>
@@ -10869,7 +11566,7 @@
         <v>30</v>
       </c>
       <c r="K160">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L160" t="s">
         <v>33</v>
@@ -10905,7 +11602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23">
       <c r="A161" t="s">
         <v>24</v>
       </c>
@@ -10925,7 +11622,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G161">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I161" t="s">
         <v>25</v>
@@ -10934,7 +11631,7 @@
         <v>30</v>
       </c>
       <c r="K161">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L161" t="s">
         <v>33</v>
@@ -10970,7 +11667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -10990,7 +11687,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G162">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I162" t="s">
         <v>25</v>
@@ -11035,7 +11732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -11055,7 +11752,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G163">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I163" t="s">
         <v>25</v>
@@ -11100,7 +11797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -11120,7 +11817,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G164">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I164" t="s">
         <v>25</v>
@@ -11165,7 +11862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -11185,7 +11882,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G165">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I165" t="s">
         <v>25</v>
@@ -11194,7 +11891,7 @@
         <v>30</v>
       </c>
       <c r="K165">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L165" t="s">
         <v>29</v>
@@ -11230,7 +11927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23">
       <c r="A166" t="s">
         <v>24</v>
       </c>
@@ -11250,7 +11947,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G166">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I166" t="s">
         <v>25</v>
@@ -11259,13 +11956,13 @@
         <v>27</v>
       </c>
       <c r="K166">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L166" t="s">
         <v>30</v>
       </c>
       <c r="M166">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N166" t="s">
         <v>29</v>
@@ -11295,7 +11992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23">
       <c r="A167" t="s">
         <v>24</v>
       </c>
@@ -11315,7 +12012,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G167">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I167" t="s">
         <v>25</v>
@@ -11360,7 +12057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23">
       <c r="A168" t="s">
         <v>24</v>
       </c>
@@ -11380,7 +12077,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G168">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I168" t="s">
         <v>25</v>
@@ -11425,7 +12122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23">
       <c r="A169" t="s">
         <v>24</v>
       </c>
@@ -11445,7 +12142,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G169">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I169" t="s">
         <v>25</v>
@@ -11490,7 +12187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23">
       <c r="A170" t="s">
         <v>24</v>
       </c>
@@ -11510,7 +12207,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G170">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I170" t="s">
         <v>25</v>
@@ -11519,7 +12216,7 @@
         <v>27</v>
       </c>
       <c r="K170">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L170" t="s">
         <v>33</v>
@@ -11531,7 +12228,7 @@
         <v>30</v>
       </c>
       <c r="O170">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q170" t="b">
         <v>0</v>
@@ -11555,7 +12252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23">
       <c r="A171" t="s">
         <v>24</v>
       </c>
@@ -11575,7 +12272,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G171">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I171" t="s">
         <v>25</v>
@@ -11620,7 +12317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23">
       <c r="A172" t="s">
         <v>24</v>
       </c>
@@ -11640,7 +12337,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G172">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I172" t="s">
         <v>25</v>
@@ -11649,7 +12346,7 @@
         <v>30</v>
       </c>
       <c r="K172">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L172" t="s">
         <v>33</v>
@@ -11685,7 +12382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23">
       <c r="A173" t="s">
         <v>24</v>
       </c>
@@ -11705,7 +12402,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G173">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I173" t="s">
         <v>25</v>
@@ -11750,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23">
       <c r="A174" t="s">
         <v>24</v>
       </c>
@@ -11770,7 +12467,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G174">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I174" t="s">
         <v>25</v>
@@ -11815,7 +12512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23">
       <c r="A175" t="s">
         <v>24</v>
       </c>
@@ -11835,7 +12532,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G175">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I175" t="s">
         <v>25</v>
@@ -11844,7 +12541,7 @@
         <v>30</v>
       </c>
       <c r="K175">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L175" t="s">
         <v>33</v>
@@ -11880,7 +12577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -11900,7 +12597,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G176">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I176" t="s">
         <v>25</v>
@@ -11945,7 +12642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23">
       <c r="A177" t="s">
         <v>24</v>
       </c>
@@ -11965,7 +12662,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G177">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I177" t="s">
         <v>25</v>
@@ -12010,7 +12707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23">
       <c r="A178" t="s">
         <v>24</v>
       </c>
@@ -12030,7 +12727,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G178">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I178" t="s">
         <v>25</v>
@@ -12039,7 +12736,7 @@
         <v>30</v>
       </c>
       <c r="K178">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L178" t="s">
         <v>33</v>
@@ -12075,7 +12772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23">
       <c r="A179" t="s">
         <v>24</v>
       </c>
@@ -12095,7 +12792,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G179">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I179" t="s">
         <v>25</v>
@@ -12140,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23">
       <c r="A180" t="s">
         <v>24</v>
       </c>
@@ -12160,7 +12857,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G180">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I180" t="s">
         <v>25</v>
@@ -12181,7 +12878,7 @@
         <v>30</v>
       </c>
       <c r="O180">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q180" t="b">
         <v>0</v>
@@ -12205,7 +12902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23">
       <c r="A181" t="s">
         <v>24</v>
       </c>
@@ -12225,7 +12922,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G181">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I181" t="s">
         <v>25</v>
@@ -12234,7 +12931,7 @@
         <v>27</v>
       </c>
       <c r="K181">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L181" t="s">
         <v>33</v>
@@ -12270,7 +12967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -12290,7 +12987,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G182">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I182" t="s">
         <v>25</v>
@@ -12335,7 +13032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23">
       <c r="A183" t="s">
         <v>24</v>
       </c>
@@ -12355,7 +13052,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G183">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I183" t="s">
         <v>25</v>
@@ -12364,7 +13061,7 @@
         <v>30</v>
       </c>
       <c r="K183">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L183" t="s">
         <v>33</v>
@@ -12400,7 +13097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23">
       <c r="A184" t="s">
         <v>24</v>
       </c>
@@ -12420,7 +13117,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G184">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I184" t="s">
         <v>25</v>
@@ -12465,7 +13162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23">
       <c r="A185" t="s">
         <v>24</v>
       </c>
@@ -12485,7 +13182,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G185">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I185" t="s">
         <v>25</v>
@@ -12494,7 +13191,7 @@
         <v>27</v>
       </c>
       <c r="K185">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L185" t="s">
         <v>33</v>
@@ -12530,7 +13227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23">
       <c r="A186" t="s">
         <v>24</v>
       </c>
@@ -12550,7 +13247,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G186">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I186" t="s">
         <v>25</v>
@@ -12559,7 +13256,7 @@
         <v>27</v>
       </c>
       <c r="K186">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L186" t="s">
         <v>29</v>
@@ -12595,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23">
       <c r="A187" t="s">
         <v>24</v>
       </c>
@@ -12615,7 +13312,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G187">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I187" t="s">
         <v>25</v>
@@ -12624,7 +13321,7 @@
         <v>30</v>
       </c>
       <c r="K187">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L187" t="s">
         <v>33</v>
@@ -12660,7 +13357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23">
       <c r="A188" t="s">
         <v>24</v>
       </c>
@@ -12680,7 +13377,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G188">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I188" t="s">
         <v>25</v>
@@ -12725,7 +13422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23">
       <c r="A189" t="s">
         <v>24</v>
       </c>
@@ -12745,7 +13442,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G189">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I189" t="s">
         <v>25</v>
@@ -12760,7 +13457,7 @@
         <v>30</v>
       </c>
       <c r="M189">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N189" t="s">
         <v>29</v>
@@ -12790,7 +13487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23">
       <c r="A190" t="s">
         <v>24</v>
       </c>
@@ -12810,7 +13507,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G190">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I190" t="s">
         <v>25</v>
@@ -12819,7 +13516,7 @@
         <v>27</v>
       </c>
       <c r="K190">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L190" t="s">
         <v>33</v>
@@ -12855,7 +13552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23">
       <c r="A191" t="s">
         <v>24</v>
       </c>
@@ -12875,7 +13572,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G191">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I191" t="s">
         <v>25</v>
@@ -12884,7 +13581,7 @@
         <v>27</v>
       </c>
       <c r="K191">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L191" t="s">
         <v>33</v>
@@ -12896,7 +13593,7 @@
         <v>30</v>
       </c>
       <c r="O191">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q191" t="b">
         <v>0</v>
@@ -12920,7 +13617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23">
       <c r="A192" t="s">
         <v>24</v>
       </c>
@@ -12940,7 +13637,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G192">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I192" t="s">
         <v>25</v>
@@ -12985,7 +13682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23">
       <c r="A193" t="s">
         <v>24</v>
       </c>
@@ -13005,7 +13702,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G193">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I193" t="s">
         <v>25</v>
@@ -13050,7 +13747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -13070,7 +13767,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G194">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I194" t="s">
         <v>25</v>
@@ -13091,7 +13788,7 @@
         <v>30</v>
       </c>
       <c r="O194">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q194" t="b">
         <v>0</v>
@@ -13115,7 +13812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23">
       <c r="A195" t="s">
         <v>24</v>
       </c>
@@ -13135,7 +13832,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G195">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I195" t="s">
         <v>25</v>
@@ -13180,7 +13877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23">
       <c r="A196" t="s">
         <v>24</v>
       </c>
@@ -13200,7 +13897,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G196">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I196" t="s">
         <v>25</v>
@@ -13245,7 +13942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23">
       <c r="A197" t="s">
         <v>24</v>
       </c>
@@ -13265,7 +13962,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G197">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I197" t="s">
         <v>25</v>
@@ -13274,7 +13971,7 @@
         <v>30</v>
       </c>
       <c r="K197">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L197" t="s">
         <v>33</v>
@@ -13310,7 +14007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23">
       <c r="A198" t="s">
         <v>24</v>
       </c>
@@ -13330,7 +14027,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G198">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I198" t="s">
         <v>25</v>
@@ -13339,7 +14036,7 @@
         <v>27</v>
       </c>
       <c r="K198">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L198" t="s">
         <v>29</v>
@@ -13375,7 +14072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -13395,7 +14092,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G199">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I199" t="s">
         <v>25</v>
@@ -13404,7 +14101,7 @@
         <v>27</v>
       </c>
       <c r="K199">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L199" t="s">
         <v>33</v>
@@ -13416,7 +14113,7 @@
         <v>27</v>
       </c>
       <c r="O199">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Q199" t="b">
         <v>0</v>
@@ -13440,7 +14137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -13460,7 +14157,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G200">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I200" t="s">
         <v>25</v>
@@ -13505,7 +14202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -13525,7 +14222,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G201">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I201" t="s">
         <v>25</v>
@@ -13540,7 +14237,7 @@
         <v>30</v>
       </c>
       <c r="M201">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N201" t="s">
         <v>29</v>
@@ -13570,7 +14267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -13590,7 +14287,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G202">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I202" t="s">
         <v>25</v>
@@ -13635,7 +14332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -13655,7 +14352,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G203">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I203" t="s">
         <v>25</v>
@@ -13700,7 +14397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -13720,7 +14417,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G204">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I204" t="s">
         <v>25</v>
@@ -13765,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -13785,7 +14482,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G205">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I205" t="s">
         <v>25</v>
@@ -13830,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23">
       <c r="A206" t="s">
         <v>24</v>
       </c>
@@ -13850,7 +14547,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G206">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I206" t="s">
         <v>25</v>
@@ -13895,7 +14592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23">
       <c r="A207" t="s">
         <v>24</v>
       </c>
@@ -13915,7 +14612,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G207">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I207" t="s">
         <v>25</v>
@@ -13960,7 +14657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23">
       <c r="A208" t="s">
         <v>24</v>
       </c>
@@ -13980,7 +14677,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G208">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I208" t="s">
         <v>25</v>
@@ -14025,7 +14722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23">
       <c r="A209" t="s">
         <v>24</v>
       </c>
@@ -14045,7 +14742,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G209">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I209" t="s">
         <v>25</v>
@@ -14090,7 +14787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23">
       <c r="A210" t="s">
         <v>24</v>
       </c>
@@ -14110,7 +14807,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G210">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I210" t="s">
         <v>25</v>
@@ -14155,7 +14852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23">
       <c r="A211" t="s">
         <v>24</v>
       </c>
@@ -14175,7 +14872,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G211">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I211" t="s">
         <v>25</v>
@@ -14184,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="K211">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L211" t="s">
         <v>33</v>
@@ -14220,7 +14917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23">
       <c r="A212" t="s">
         <v>24</v>
       </c>
@@ -14240,7 +14937,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G212">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I212" t="s">
         <v>25</v>
@@ -14249,13 +14946,13 @@
         <v>27</v>
       </c>
       <c r="K212">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L212" t="s">
         <v>30</v>
       </c>
       <c r="M212">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N212" t="s">
         <v>29</v>
@@ -14285,7 +14982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23">
       <c r="A213" t="s">
         <v>24</v>
       </c>
@@ -14305,7 +15002,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G213">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I213" t="s">
         <v>25</v>
@@ -14350,7 +15047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23">
       <c r="A214" t="s">
         <v>24</v>
       </c>
@@ -14370,7 +15067,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G214">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I214" t="s">
         <v>25</v>
@@ -14385,7 +15082,7 @@
         <v>30</v>
       </c>
       <c r="M214">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N214" t="s">
         <v>29</v>
@@ -14415,7 +15112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23">
       <c r="A215" t="s">
         <v>24</v>
       </c>
@@ -14435,7 +15132,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G215">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I215" t="s">
         <v>25</v>
@@ -14480,7 +15177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23">
       <c r="A216" t="s">
         <v>24</v>
       </c>
@@ -14500,7 +15197,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G216">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I216" t="s">
         <v>25</v>
@@ -14545,7 +15242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23">
       <c r="A217" t="s">
         <v>24</v>
       </c>
@@ -14565,7 +15262,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G217">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I217" t="s">
         <v>25</v>
@@ -14574,7 +15271,7 @@
         <v>30</v>
       </c>
       <c r="K217">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L217" t="s">
         <v>33</v>
@@ -14610,7 +15307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23">
       <c r="A218" t="s">
         <v>24</v>
       </c>
@@ -14630,7 +15327,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G218">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I218" t="s">
         <v>25</v>
@@ -14651,7 +15348,7 @@
         <v>30</v>
       </c>
       <c r="O218">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q218" t="b">
         <v>0</v>
@@ -14675,7 +15372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23">
       <c r="A219" t="s">
         <v>24</v>
       </c>
@@ -14695,7 +15392,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G219">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I219" t="s">
         <v>25</v>
@@ -14740,7 +15437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23">
       <c r="A220" t="s">
         <v>24</v>
       </c>
@@ -14760,7 +15457,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G220">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I220" t="s">
         <v>25</v>
@@ -14805,7 +15502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23">
       <c r="A221" t="s">
         <v>24</v>
       </c>
@@ -14825,7 +15522,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G221">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I221" t="s">
         <v>25</v>
@@ -14846,7 +15543,7 @@
         <v>27</v>
       </c>
       <c r="O221">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Q221" t="b">
         <v>0</v>
@@ -14870,7 +15567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23">
       <c r="A222" t="s">
         <v>24</v>
       </c>
@@ -14890,7 +15587,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G222">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I222" t="s">
         <v>25</v>
@@ -14935,7 +15632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23">
       <c r="A223" t="s">
         <v>24</v>
       </c>
@@ -14955,7 +15652,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G223">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I223" t="s">
         <v>25</v>
@@ -14964,7 +15661,7 @@
         <v>30</v>
       </c>
       <c r="K223">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L223" t="s">
         <v>33</v>
@@ -15000,7 +15697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23">
       <c r="A224" t="s">
         <v>24</v>
       </c>
@@ -15020,7 +15717,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G224">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I224" t="s">
         <v>25</v>
@@ -15029,7 +15726,7 @@
         <v>30</v>
       </c>
       <c r="K224">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L224" t="s">
         <v>33</v>
@@ -15065,7 +15762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23">
       <c r="A225" t="s">
         <v>24</v>
       </c>
@@ -15085,7 +15782,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G225">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I225" t="s">
         <v>25</v>
@@ -15130,7 +15827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23">
       <c r="A226" t="s">
         <v>24</v>
       </c>
@@ -15150,7 +15847,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G226">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I226" t="s">
         <v>25</v>
@@ -15195,7 +15892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23">
       <c r="A227" t="s">
         <v>24</v>
       </c>
@@ -15215,7 +15912,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G227">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I227" t="s">
         <v>25</v>
@@ -15224,7 +15921,7 @@
         <v>30</v>
       </c>
       <c r="K227">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L227" t="s">
         <v>33</v>
@@ -15260,7 +15957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23">
       <c r="A228" t="s">
         <v>24</v>
       </c>
@@ -15280,7 +15977,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G228">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I228" t="s">
         <v>25</v>
@@ -15325,7 +16022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23">
       <c r="A229" t="s">
         <v>24</v>
       </c>
@@ -15345,7 +16042,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G229">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I229" t="s">
         <v>25</v>
@@ -15390,7 +16087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23">
       <c r="A230" t="s">
         <v>24</v>
       </c>
@@ -15410,7 +16107,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G230">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I230" t="s">
         <v>25</v>
@@ -15455,7 +16152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23">
       <c r="A231" t="s">
         <v>24</v>
       </c>
@@ -15475,7 +16172,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G231">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I231" t="s">
         <v>25</v>
@@ -15484,7 +16181,7 @@
         <v>27</v>
       </c>
       <c r="K231">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="L231" t="s">
         <v>33</v>
@@ -15520,7 +16217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23">
       <c r="A232" t="s">
         <v>24</v>
       </c>
@@ -15540,7 +16237,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G232">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I232" t="s">
         <v>25</v>
@@ -15549,7 +16246,7 @@
         <v>30</v>
       </c>
       <c r="K232">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L232" t="s">
         <v>33</v>
@@ -15585,7 +16282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23">
       <c r="A233" t="s">
         <v>24</v>
       </c>
@@ -15605,7 +16302,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G233">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I233" t="s">
         <v>25</v>
@@ -15650,7 +16347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23">
       <c r="A234" t="s">
         <v>24</v>
       </c>
@@ -15670,7 +16367,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G234">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I234" t="s">
         <v>25</v>
@@ -15679,7 +16376,7 @@
         <v>30</v>
       </c>
       <c r="K234">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L234" t="s">
         <v>33</v>
@@ -15715,7 +16412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23">
       <c r="A235" t="s">
         <v>24</v>
       </c>
@@ -15735,7 +16432,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G235">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I235" t="s">
         <v>25</v>
@@ -15756,7 +16453,7 @@
         <v>30</v>
       </c>
       <c r="O235">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q235" t="b">
         <v>0</v>
@@ -15780,7 +16477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23">
       <c r="A236" t="s">
         <v>24</v>
       </c>
@@ -15800,7 +16497,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G236">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I236" t="s">
         <v>25</v>
@@ -15809,7 +16506,7 @@
         <v>30</v>
       </c>
       <c r="K236">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L236" t="s">
         <v>33</v>
@@ -15845,7 +16542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23">
       <c r="A237" t="s">
         <v>24</v>
       </c>
@@ -15865,7 +16562,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G237">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I237" t="s">
         <v>25</v>
@@ -15874,7 +16571,7 @@
         <v>30</v>
       </c>
       <c r="K237">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L237" t="s">
         <v>33</v>
@@ -15910,7 +16607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23">
       <c r="A238" t="s">
         <v>24</v>
       </c>
@@ -15930,7 +16627,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G238">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I238" t="s">
         <v>25</v>
@@ -15945,7 +16642,7 @@
         <v>30</v>
       </c>
       <c r="M238">
-        <v>0.14285714285714279</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N238" t="s">
         <v>29</v>
@@ -15975,7 +16672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23">
       <c r="A239" t="s">
         <v>24</v>
       </c>
@@ -15995,7 +16692,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G239">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I239" t="s">
         <v>25</v>
@@ -16040,7 +16737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23">
       <c r="A240" t="s">
         <v>24</v>
       </c>
@@ -16060,7 +16757,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G240">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I240" t="s">
         <v>25</v>
@@ -16105,7 +16802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23">
       <c r="A241" t="s">
         <v>24</v>
       </c>
@@ -16125,7 +16822,7 @@
         <v>14.58716155891277</v>
       </c>
       <c r="G241">
-        <v>6.8042518700701224</v>
+        <v>6.804251870070122</v>
       </c>
       <c r="I241" t="s">
         <v>25</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
@@ -600,10 +600,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>7</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1026,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1168,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1236,13 +1236,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="b">
         <v>1</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="b">
         <v>1</v>
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="b">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1736,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1804,13 +1804,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -1878,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2120,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
         <v>1</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
         <v>1</v>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
         <v>1</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
         <v>1</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -2514,10 +2514,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
         <v>1</v>
@@ -2526,7 +2526,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
         <v>1</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
         <v>1</v>
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
         <v>1</v>
@@ -3014,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36">
         <v>7</v>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
@@ -3295,13 +3295,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40">
         <v>7</v>
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="D41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>7</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="b">
         <v>1</v>
@@ -3378,7 +3378,7 @@
         <v>7</v>
       </c>
       <c r="U41">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3440,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43">
         <v>7</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -3866,10 +3866,10 @@
         <v>0</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48">
         <v>7</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="b">
         <v>1</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>1</v>
@@ -4079,10 +4079,10 @@
         <v>0</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51">
         <v>7</v>
@@ -4108,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="D52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>7</v>
@@ -4147,10 +4147,10 @@
         <v>0</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="b">
         <v>1</v>
@@ -4159,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="U52">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="V52">
         <v>7</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="b">
         <v>1</v>
@@ -4321,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>7</v>
@@ -4360,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>7</v>
       </c>
       <c r="U55">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="V55">
         <v>7</v>
@@ -4434,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56">
         <v>7</v>
@@ -4534,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -4573,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="b">
         <v>1</v>
@@ -4585,7 +4585,7 @@
         <v>7</v>
       </c>
       <c r="U58">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="V58">
         <v>7</v>
@@ -4718,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="b">
         <v>1</v>
@@ -4789,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61">
         <v>7</v>
@@ -4860,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="R62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62">
         <v>7</v>
@@ -4928,13 +4928,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63">
         <v>7</v>
@@ -5073,10 +5073,10 @@
         <v>0</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65">
         <v>7</v>
@@ -5212,13 +5212,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67">
         <v>7</v>
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
         <v>1</v>
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="b">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="b">
         <v>1</v>
@@ -5570,10 +5570,10 @@
         <v>0</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72">
         <v>7</v>
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="b">
         <v>1</v>
@@ -5712,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
         <v>1</v>
@@ -5783,10 +5783,10 @@
         <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75">
         <v>7</v>
@@ -5854,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76">
         <v>7</v>
@@ -5922,13 +5922,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77">
         <v>7</v>
@@ -6067,10 +6067,10 @@
         <v>0</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79">
         <v>7</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
         <v>1</v>
@@ -6280,10 +6280,10 @@
         <v>0</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82">
         <v>7</v>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="b">
         <v>1</v>
@@ -6422,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="b">
         <v>1</v>
@@ -6493,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85">
         <v>7</v>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="b">
         <v>1</v>
@@ -6635,10 +6635,10 @@
         <v>0</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87">
         <v>7</v>
@@ -6706,10 +6706,10 @@
         <v>0</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88">
         <v>7</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="b">
         <v>1</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="b">
         <v>1</v>
@@ -7203,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="b">
         <v>1</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="b">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>1</v>
       </c>
       <c r="D97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>7</v>
@@ -7342,10 +7342,10 @@
         <v>0</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="b">
         <v>1</v>
@@ -7354,7 +7354,7 @@
         <v>7</v>
       </c>
       <c r="U97">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="V97">
         <v>7</v>
@@ -7416,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="b">
         <v>1</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99">
         <v>7</v>
@@ -7558,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="b">
         <v>1</v>
@@ -7629,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101">
         <v>7</v>
@@ -7700,10 +7700,10 @@
         <v>0</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102">
         <v>7</v>
@@ -7768,13 +7768,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103">
         <v>7</v>
@@ -7800,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -7839,10 +7839,10 @@
         <v>0</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" t="b">
         <v>1</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="U104">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="V104">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="R105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S105" t="b">
         <v>1</v>
@@ -8052,13 +8052,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107">
         <v>7</v>
@@ -8126,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="R108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108">
         <v>7</v>
@@ -8197,10 +8197,10 @@
         <v>0</v>
       </c>
       <c r="R109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109">
         <v>7</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="R111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111">
         <v>7</v>
@@ -8368,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>7</v>
@@ -8407,10 +8407,10 @@
         <v>0</v>
       </c>
       <c r="Q112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S112" t="b">
         <v>1</v>
@@ -8419,7 +8419,7 @@
         <v>7</v>
       </c>
       <c r="U112">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="V112">
         <v>7</v>
@@ -8481,10 +8481,10 @@
         <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113">
         <v>7</v>
@@ -8510,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>7</v>
@@ -8549,10 +8549,10 @@
         <v>0</v>
       </c>
       <c r="Q114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" t="b">
         <v>1</v>
@@ -8561,7 +8561,7 @@
         <v>7</v>
       </c>
       <c r="U114">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V114">
         <v>7</v>
@@ -8623,7 +8623,7 @@
         <v>0</v>
       </c>
       <c r="R115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="b">
         <v>1</v>
@@ -8691,13 +8691,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116">
         <v>7</v>
@@ -8762,13 +8762,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117">
         <v>7</v>
@@ -8907,10 +8907,10 @@
         <v>0</v>
       </c>
       <c r="R119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119">
         <v>7</v>
@@ -8978,10 +8978,10 @@
         <v>0</v>
       </c>
       <c r="R120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>0</v>
       </c>
       <c r="R121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121">
         <v>7</v>
@@ -9114,10 +9114,10 @@
         <v>0</v>
       </c>
       <c r="R122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122">
         <v>7</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124">
         <v>7</v>
@@ -9374,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="R126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S126" t="b">
         <v>1</v>
@@ -9439,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127">
         <v>7</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128">
         <v>7</v>
@@ -9634,10 +9634,10 @@
         <v>0</v>
       </c>
       <c r="R130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130">
         <v>7</v>
@@ -9699,10 +9699,10 @@
         <v>0</v>
       </c>
       <c r="R131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131">
         <v>7</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>7</v>
@@ -9764,7 +9764,7 @@
         <v>1</v>
       </c>
       <c r="R132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S132" t="b">
         <v>1</v>
@@ -9773,7 +9773,7 @@
         <v>7</v>
       </c>
       <c r="U132">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="V132">
         <v>7</v>
@@ -9858,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>7</v>
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="R134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S134" t="b">
         <v>1</v>
@@ -9903,7 +9903,7 @@
         <v>7</v>
       </c>
       <c r="U134">
-        <v>687</v>
+        <v>0</v>
       </c>
       <c r="V134">
         <v>7</v>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="R136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S136" t="b">
         <v>1</v>
@@ -10089,10 +10089,10 @@
         <v>0</v>
       </c>
       <c r="R137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>0</v>
       </c>
       <c r="R138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138">
         <v>7</v>
@@ -10219,10 +10219,10 @@
         <v>0</v>
       </c>
       <c r="R139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139">
         <v>7</v>
@@ -10284,10 +10284,10 @@
         <v>0</v>
       </c>
       <c r="R140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T140">
         <v>7</v>
@@ -10349,10 +10349,10 @@
         <v>0</v>
       </c>
       <c r="R141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141">
         <v>7</v>
@@ -10544,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S144" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="R145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S145" t="b">
         <v>1</v>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="R146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S146" t="b">
         <v>1</v>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="R147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S147" t="b">
         <v>1</v>
@@ -10804,7 +10804,7 @@
         <v>0</v>
       </c>
       <c r="R148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S148" t="b">
         <v>1</v>
@@ -10869,7 +10869,7 @@
         <v>0</v>
       </c>
       <c r="R149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S149" t="b">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="R150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S150" t="b">
         <v>1</v>
@@ -10999,10 +10999,10 @@
         <v>0</v>
       </c>
       <c r="R151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T151">
         <v>7</v>
@@ -11064,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="R152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S152" t="b">
         <v>1</v>
@@ -11129,10 +11129,10 @@
         <v>0</v>
       </c>
       <c r="R153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="R154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S154" t="b">
         <v>1</v>
@@ -11259,7 +11259,7 @@
         <v>0</v>
       </c>
       <c r="R155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S155" t="b">
         <v>1</v>
@@ -11324,10 +11324,10 @@
         <v>0</v>
       </c>
       <c r="R156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156">
         <v>7</v>
@@ -11454,7 +11454,7 @@
         <v>0</v>
       </c>
       <c r="R158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S158" t="b">
         <v>1</v>
@@ -11584,10 +11584,10 @@
         <v>0</v>
       </c>
       <c r="R160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160">
         <v>7</v>
@@ -11649,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="R161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S161" t="b">
         <v>1</v>
@@ -11714,10 +11714,10 @@
         <v>0</v>
       </c>
       <c r="R162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T162">
         <v>7</v>
@@ -11779,10 +11779,10 @@
         <v>0</v>
       </c>
       <c r="R163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T163">
         <v>7</v>
@@ -12104,10 +12104,10 @@
         <v>0</v>
       </c>
       <c r="R168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T168">
         <v>7</v>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="R169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S169" t="b">
         <v>1</v>
@@ -12234,7 +12234,7 @@
         <v>0</v>
       </c>
       <c r="R170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="b">
         <v>1</v>
@@ -12299,10 +12299,10 @@
         <v>0</v>
       </c>
       <c r="R171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171">
         <v>7</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="R172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S172" t="b">
         <v>1</v>
@@ -12494,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="R174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S174" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="R175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S175" t="b">
         <v>1</v>
@@ -12624,10 +12624,10 @@
         <v>0</v>
       </c>
       <c r="R176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176">
         <v>7</v>
@@ -12754,7 +12754,7 @@
         <v>0</v>
       </c>
       <c r="R178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S178" t="b">
         <v>1</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="R180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S180" t="b">
         <v>1</v>
@@ -12949,10 +12949,10 @@
         <v>0</v>
       </c>
       <c r="R181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T181">
         <v>7</v>
@@ -13014,10 +13014,10 @@
         <v>0</v>
       </c>
       <c r="R182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T182">
         <v>7</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="R183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183">
         <v>7</v>
@@ -13209,10 +13209,10 @@
         <v>0</v>
       </c>
       <c r="R185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T185">
         <v>7</v>
@@ -13339,10 +13339,10 @@
         <v>0</v>
       </c>
       <c r="R187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T187">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S188" t="b">
         <v>1</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S190" t="b">
         <v>1</v>
@@ -13599,7 +13599,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S191" t="b">
         <v>1</v>
@@ -13664,10 +13664,10 @@
         <v>0</v>
       </c>
       <c r="R192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192">
         <v>7</v>
@@ -13729,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S193" t="b">
         <v>1</v>
@@ -13794,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="b">
         <v>1</v>
@@ -13859,10 +13859,10 @@
         <v>0</v>
       </c>
       <c r="R195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T195">
         <v>7</v>
@@ -13924,10 +13924,10 @@
         <v>0</v>
       </c>
       <c r="R196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T196">
         <v>7</v>
@@ -13989,10 +13989,10 @@
         <v>0</v>
       </c>
       <c r="R197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T197">
         <v>7</v>
@@ -14119,10 +14119,10 @@
         <v>0</v>
       </c>
       <c r="R199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T199">
         <v>7</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="R200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S200" t="b">
         <v>1</v>
@@ -14314,10 +14314,10 @@
         <v>0</v>
       </c>
       <c r="R202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T202">
         <v>7</v>
@@ -14379,7 +14379,7 @@
         <v>0</v>
       </c>
       <c r="R203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S203" t="b">
         <v>1</v>
@@ -14444,7 +14444,7 @@
         <v>0</v>
       </c>
       <c r="R204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S204" t="b">
         <v>1</v>
@@ -14509,10 +14509,10 @@
         <v>0</v>
       </c>
       <c r="R205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T205">
         <v>7</v>
@@ -14574,7 +14574,7 @@
         <v>0</v>
       </c>
       <c r="R206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S206" t="b">
         <v>1</v>
@@ -14639,10 +14639,10 @@
         <v>0</v>
       </c>
       <c r="R207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T207">
         <v>7</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="R208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T208">
         <v>7</v>
@@ -14769,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="R209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S209" t="b">
         <v>1</v>
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="R211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S211" t="b">
         <v>1</v>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="R213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S213" t="b">
         <v>1</v>
@@ -15159,7 +15159,7 @@
         <v>0</v>
       </c>
       <c r="R215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S215" t="b">
         <v>1</v>
@@ -15224,7 +15224,7 @@
         <v>0</v>
       </c>
       <c r="R216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S216" t="b">
         <v>1</v>
@@ -15289,7 +15289,7 @@
         <v>0</v>
       </c>
       <c r="R217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S217" t="b">
         <v>1</v>
@@ -15354,7 +15354,7 @@
         <v>0</v>
       </c>
       <c r="R218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S218" t="b">
         <v>1</v>
@@ -15419,10 +15419,10 @@
         <v>0</v>
       </c>
       <c r="R219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T219">
         <v>7</v>
@@ -15484,7 +15484,7 @@
         <v>0</v>
       </c>
       <c r="R220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S220" t="b">
         <v>1</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="R221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T221">
         <v>7</v>
@@ -15614,10 +15614,10 @@
         <v>0</v>
       </c>
       <c r="R222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T222">
         <v>7</v>
@@ -15679,10 +15679,10 @@
         <v>0</v>
       </c>
       <c r="R223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T223">
         <v>7</v>
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="R224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S224" t="b">
         <v>1</v>
@@ -15809,7 +15809,7 @@
         <v>0</v>
       </c>
       <c r="R225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S225" t="b">
         <v>1</v>
@@ -15939,10 +15939,10 @@
         <v>0</v>
       </c>
       <c r="R227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T227">
         <v>7</v>
@@ -16004,10 +16004,10 @@
         <v>0</v>
       </c>
       <c r="R228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T228">
         <v>7</v>
@@ -16069,10 +16069,10 @@
         <v>0</v>
       </c>
       <c r="R229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T229">
         <v>7</v>
@@ -16199,10 +16199,10 @@
         <v>0</v>
       </c>
       <c r="R231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T231">
         <v>7</v>
@@ -16264,7 +16264,7 @@
         <v>0</v>
       </c>
       <c r="R232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S232" t="b">
         <v>1</v>
@@ -16329,10 +16329,10 @@
         <v>0</v>
       </c>
       <c r="R233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T233">
         <v>7</v>
@@ -16394,7 +16394,7 @@
         <v>0</v>
       </c>
       <c r="R234" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S234" t="b">
         <v>1</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="R235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S235" t="b">
         <v>1</v>
@@ -16524,10 +16524,10 @@
         <v>0</v>
       </c>
       <c r="R236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T236">
         <v>7</v>
@@ -16589,10 +16589,10 @@
         <v>0</v>
       </c>
       <c r="R237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T237">
         <v>7</v>
@@ -16719,10 +16719,10 @@
         <v>0</v>
       </c>
       <c r="R239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T239">
         <v>7</v>
@@ -16784,10 +16784,10 @@
         <v>0</v>
       </c>
       <c r="R240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T240">
         <v>7</v>
@@ -16849,10 +16849,10 @@
         <v>0</v>
       </c>
       <c r="R241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T241">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_us_crime.xlsx
@@ -88,10 +88,10 @@
     <t>cant_min_en_p_elegido</t>
   </si>
   <si>
-    <t>D35_R35_Pentropia</t>
+    <t>PRD35_PR35_CPent_UD080_PE45</t>
   </si>
   <si>
-    <t>D35_R35_Pproporcion</t>
+    <t>PRD35_PR35_CPprop_UD080_Ppp041</t>
   </si>
   <si>
     <t>proporcion</t>
